--- a/docs/Shopify_Deal_Workbook_v4.xlsx
+++ b/docs/Shopify_Deal_Workbook_v4.xlsx
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
@@ -41,8 +41,10 @@
     <numFmt numFmtId="178" formatCode="+0.000x;-0.000x"/>
     <numFmt numFmtId="179" formatCode="0.00&quot;×&quot;"/>
     <numFmt numFmtId="180" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="181" formatCode="#,##0.000"/>
+    <numFmt numFmtId="182" formatCode="0.000&quot;x&quot;"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -283,6 +285,12 @@
       <b val="1"/>
       <color rgb="00444444"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4761"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="19">
@@ -600,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="403">
+  <cellXfs count="420">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1714,6 +1722,57 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="41" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="19" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="19" fillId="13" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="20" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="20" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="18" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="8" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="43" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2991,7 +3050,7 @@
           <t>Holding Period (Years)</t>
         </is>
       </c>
-      <c r="C35" s="109">
+      <c r="C35" s="346">
         <f>IFERROR(C11-C10,"-")</f>
         <v/>
       </c>
@@ -9013,12 +9072,12 @@
           <t>NTB-1: GMV Sustains 25%+ Through FY2027</t>
         </is>
       </c>
-      <c r="C8" s="196">
-        <f>IFERROR('NTB REGISTRY'!F8,"-")</f>
-        <v/>
-      </c>
-      <c r="D8" s="207">
-        <f>IFERROR('NTB REGISTRY'!G8,"-")</f>
+      <c r="C8" s="403">
+        <f>IFERROR('NTB REGISTRY'!E7,"-")</f>
+        <v/>
+      </c>
+      <c r="D8" s="404">
+        <f>IFERROR('NTB REGISTRY'!F7,"-")</f>
         <v/>
       </c>
       <c r="E8" s="208">
@@ -9032,12 +9091,12 @@
           <t>NTB-2: Payments GPV Penetration to 70%+</t>
         </is>
       </c>
-      <c r="C9" s="209">
-        <f>IFERROR('NTB REGISTRY'!F9,"-")</f>
-        <v/>
-      </c>
-      <c r="D9" s="210">
-        <f>IFERROR('NTB REGISTRY'!G9,"-")</f>
+      <c r="C9" s="405">
+        <f>IFERROR('NTB REGISTRY'!E8,"-")</f>
+        <v/>
+      </c>
+      <c r="D9" s="406">
+        <f>IFERROR('NTB REGISTRY'!F8,"-")</f>
         <v/>
       </c>
       <c r="E9" s="211">
@@ -9051,12 +9110,12 @@
           <t>NTB-3: AI Commerce Net Revenue-Positive</t>
         </is>
       </c>
-      <c r="C10" s="196">
-        <f>IFERROR('NTB REGISTRY'!F10,"-")</f>
-        <v/>
-      </c>
-      <c r="D10" s="207">
-        <f>IFERROR('NTB REGISTRY'!G10,"-")</f>
+      <c r="C10" s="403">
+        <f>IFERROR('NTB REGISTRY'!E9,"-")</f>
+        <v/>
+      </c>
+      <c r="D10" s="404">
+        <f>IFERROR('NTB REGISTRY'!F9,"-")</f>
         <v/>
       </c>
       <c r="E10" s="208">
@@ -9070,12 +9129,12 @@
           <t>NTB-4: Enterprise Plus Margin Durable</t>
         </is>
       </c>
-      <c r="C11" s="209">
-        <f>IFERROR('NTB REGISTRY'!F11,"-")</f>
-        <v/>
-      </c>
-      <c r="D11" s="210">
-        <f>IFERROR('NTB REGISTRY'!G11,"-")</f>
+      <c r="C11" s="405">
+        <f>IFERROR('NTB REGISTRY'!E10,"-")</f>
+        <v/>
+      </c>
+      <c r="D11" s="406">
+        <f>IFERROR('NTB REGISTRY'!F10,"-")</f>
         <v/>
       </c>
       <c r="E11" s="211">
@@ -9086,16 +9145,14 @@
     <row r="12" ht="15" customHeight="1">
       <c r="B12" s="92" t="inlineStr">
         <is>
-          <t>NTB-5: FCF Margin Expands to 20%+</t>
-        </is>
-      </c>
-      <c r="C12" s="196">
-        <f>IFERROR('NTB REGISTRY'!F12,"-")</f>
-        <v/>
-      </c>
-      <c r="D12" s="207">
-        <f>IFERROR('NTB REGISTRY'!G12,"-")</f>
-        <v/>
+          <t>NTB-5: FCF Margin Expands to 20%+  [not modeled in base case]</t>
+        </is>
+      </c>
+      <c r="C12" s="403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="404" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="208">
         <f>IFERROR(E11+D12,"-")</f>
@@ -9105,16 +9162,14 @@
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="94" t="inlineStr">
         <is>
-          <t>NTB-6: Macro Does Not Materially Deteriorate</t>
-        </is>
-      </c>
-      <c r="C13" s="209">
-        <f>IFERROR('NTB REGISTRY'!F13,"-")</f>
-        <v/>
-      </c>
-      <c r="D13" s="210">
-        <f>IFERROR('NTB REGISTRY'!G13,"-")</f>
-        <v/>
+          <t>NTB-6: Macro Does Not Materially Deteriorate  [not modeled in base case]</t>
+        </is>
+      </c>
+      <c r="C13" s="405" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="406" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="211">
         <f>IFERROR(E12+D13,"-")</f>
@@ -9122,27 +9177,46 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="212" t="inlineStr">
-        <is>
-          <t>Multiple Re-rating / Compression (net)</t>
-        </is>
-      </c>
-      <c r="C14" s="213" t="n"/>
-      <c r="D14" s="214" t="n"/>
-      <c r="E14" s="215">
+      <c r="B14" s="407" t="inlineStr">
+        <is>
+          <t>Multiple Re-rating / Compression  (48.5x entry to 45.0x exit x $4.7B exit EBITDA)</t>
+        </is>
+      </c>
+      <c r="C14" s="408">
+        <f>'DRIVER TREE'!L31</f>
+        <v/>
+      </c>
+      <c r="D14" s="409">
+        <f>'DRIVER TREE'!N31</f>
+        <v/>
+      </c>
+      <c r="E14" s="410">
         <f>IFERROR(E13+D14,"-")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="12" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="87" t="n"/>
-      <c r="B15" s="87" t="n"/>
-      <c r="C15" s="87" t="n"/>
-      <c r="D15" s="87" t="n"/>
-      <c r="E15" s="87" t="n"/>
-      <c r="F15" s="87" t="n"/>
-      <c r="G15" s="87" t="n"/>
-      <c r="H15" s="87" t="n"/>
+      <c r="B15" s="411" t="inlineStr">
+        <is>
+          <t>Net Cash Build  (Net cash $6.3B to $12.4B; INPUTS rows 20 / 29)</t>
+        </is>
+      </c>
+      <c r="C15" s="412">
+        <f>'DRIVER TREE'!L32</f>
+        <v/>
+      </c>
+      <c r="D15" s="413">
+        <f>'DRIVER TREE'!N32</f>
+        <v/>
+      </c>
+      <c r="E15" s="414">
+        <f>IFERROR(E14+D15,"-")</f>
+        <v/>
+      </c>
+      <c r="F15" s="270" t="n"/>
+      <c r="G15" s="270" t="n"/>
+      <c r="H15" s="270" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="90" t="inlineStr">
@@ -9217,7 +9291,7 @@
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="222" t="inlineStr">
+      <c r="B5" s="348" t="inlineStr">
         <is>
           <t>NTB REGISTRY  —  THESIS TO VALUE ATTRIBUTION</t>
         </is>
@@ -9303,11 +9377,13 @@
           <t>Thesis: Multiple independent GMV growth vectors (same-cohort expansion, new merchant acquisition, geographic expansion to 15 intl markets, B2B +80% YoY) sustain 20-22% GMV CAGR through FY2028E vs. consensus expectation of GMV deceleration driven by FX and tougher comps. Key: geographic and B2B channels reduce single-point-of-failure risk. [IC Memo: Pillar 1 — LOW evidence strength, THESIS-CRITICAL]</t>
         </is>
       </c>
-      <c r="E7" s="290" t="n">
-        <v>55427.927</v>
-      </c>
-      <c r="F7" s="291" t="n">
-        <v>0.392</v>
+      <c r="E7" s="415">
+        <f>'DRIVER TREE'!M13+'DRIVER TREE'!M16+'DRIVER TREE'!M23</f>
+        <v/>
+      </c>
+      <c r="F7" s="291">
+        <f>IFERROR(E7/INPUTS!$C$21,"-")</f>
+        <v/>
       </c>
       <c r="G7" s="292" t="n">
         <v>72056.306</v>
@@ -9348,11 +9424,13 @@
           <t>Thesis: GPV penetration grows 71% → 79% FY2026-28E driven by Shop Pay expansion on non-Shopify storefronts, checkout optimization, and merchant incentives. Each 100bps penetration = $124M incremental revenue at exit GMV ($699.6B). Model assumes 8pp penetration gain; consensus (sell-side avg) ~74% FY2028E implies 5pp below model — model is already thesis-aligned. Non-payments (MCA, Balance) add $268M incremental. [IC Memo: Pillar 2 — HIGH evidence strength, Payments thesis CONFIRMED]</t>
         </is>
       </c>
-      <c r="E8" s="298" t="n">
-        <v>13067.341</v>
-      </c>
-      <c r="F8" s="299" t="n">
-        <v>0.092</v>
+      <c r="E8" s="416">
+        <f>'DRIVER TREE'!M15</f>
+        <v/>
+      </c>
+      <c r="F8" s="299">
+        <f>IFERROR(E8/INPUTS!$C$21,"-")</f>
+        <v/>
       </c>
       <c r="G8" s="300" t="n">
         <v>18294.277</v>
@@ -9393,7 +9471,7 @@
           <t>Thesis: Shopify's 20+ year proprietary commerce data creates a structural moat vs. general-purpose AI (2× conversion rate on AI-assisted orders vs. organic search Q1'26). AI revenue streams (Sidekick subscription, Usage-based Commerce Protocols) not yet in base model — pure optionality upside. No FY2028E base case contribution modeled. Upside scenario: $40B EV ($15B Sidekick + $25B UCP). [IC Memo: Pillar 3 — MEDIUM evidence strength, THESIS-CRITICAL for long-term]</t>
         </is>
       </c>
-      <c r="E9" s="290" t="n">
+      <c r="E9" s="415" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="304" t="n">
@@ -9438,11 +9516,13 @@
           <t>Thesis: $25M+ GMV cohort is fastest-growing segment Q1'26 with no SMB cannibalization. Plus MRR grows from $83.6M (FY2026E, 35% of MRR) to $114.5M (FY2028E, 39% of MRR) driving $427M incremental subscription revenue at ~82% gross margin. High-margin subscription mix shift benefits blended margins. Upside: Plus penetration accelerates to 45% of MRR ($137M) by FY2028E. [IC Memo: Pillar 4 — MEDIUM evidence strength, VALUATION OPTIONALITY]</t>
         </is>
       </c>
-      <c r="E10" s="298" t="n">
-        <v>23420.507</v>
-      </c>
-      <c r="F10" s="299" t="n">
-        <v>0.165</v>
+      <c r="E10" s="416">
+        <f>'DRIVER TREE'!M22</f>
+        <v/>
+      </c>
+      <c r="F10" s="299">
+        <f>IFERROR(E10/INPUTS!$C$21,"-")</f>
+        <v/>
       </c>
       <c r="G10" s="300" t="n">
         <v>31617.684</v>
@@ -9483,11 +9563,13 @@
           <t>Risk: Entry at 48.5× EV/EBITDA creates structural headwind. Exit at 45× already assumes compression. Each 1× turn of additional compression = $4,687M additional EV reduction = -0.033x MOIC drag. Downside scenario: exit at 40× → additional -$23.4B EV → MOIC = 1.41× (vs. 1.58× base). Offsetting factor: EBITDA growth nearly triples ($2.79B → $4.69B), supporting multiple. [Macro risk: consumer softness, tariff impact on SMB GMV]</t>
         </is>
       </c>
-      <c r="E11" s="308" t="n">
-        <v>-16404.5</v>
-      </c>
-      <c r="F11" s="304" t="n">
-        <v>-0.116</v>
+      <c r="E11" s="417">
+        <f>'DRIVER TREE'!L31</f>
+        <v/>
+      </c>
+      <c r="F11" s="304">
+        <f>IFERROR(E11/INPUTS!$C$21,"-")</f>
+        <v/>
       </c>
       <c r="G11" s="308" t="n">
         <v>-8202.25</v>
@@ -9518,17 +9600,19 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12" s="263" t="inlineStr">
+      <c r="C12" s="379" t="inlineStr">
         <is>
           <t>Base + Multiple Compression + Net Cash</t>
         </is>
       </c>
       <c r="D12" s="282" t="n"/>
-      <c r="E12" s="311" t="n">
-        <v>81626.27</v>
-      </c>
-      <c r="F12" s="312" t="n">
-        <v>0.58</v>
+      <c r="E12" s="418">
+        <f>SUM(E7:E11)+'DRIVER TREE'!L32</f>
+        <v/>
+      </c>
+      <c r="F12" s="385">
+        <f>IFERROR(E12/INPUTS!$C$21,"-")</f>
+        <v/>
       </c>
       <c r="G12" s="282" t="n"/>
       <c r="H12" s="282" t="n"/>
@@ -9547,8 +9631,9 @@
       </c>
       <c r="D13" s="279" t="n"/>
       <c r="E13" s="279" t="n"/>
-      <c r="F13" s="315" t="n">
-        <v>1.577</v>
+      <c r="F13" s="419">
+        <f>IFERROR(1+F12,"-")</f>
+        <v/>
       </c>
       <c r="G13" s="279" t="n"/>
       <c r="H13" s="279" t="n"/>
